--- a/SCE_stdev.xlsx
+++ b/SCE_stdev.xlsx
@@ -75,7 +75,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -148,13 +148,13 @@
         <v>4.3766160011291504</v>
       </c>
       <c r="C7" s="2">
-        <v>4.3250417709350586</v>
+        <v>4.322415828704834</v>
       </c>
       <c r="D7" s="2">
         <v>5.3208756446838379</v>
       </c>
       <c r="E7" s="2">
-        <v>5.1943440437316895</v>
+        <v>5.1947240829467773</v>
       </c>
     </row>
     <row r="8">
@@ -165,13 +165,13 @@
         <v>4.9273009300231934</v>
       </c>
       <c r="C8" s="2">
-        <v>4.8050918579101562</v>
+        <v>4.799527645111084</v>
       </c>
       <c r="D8" s="2">
         <v>5.6248149871826172</v>
       </c>
       <c r="E8" s="2">
-        <v>5.5279655456542969</v>
+        <v>5.5266070365905762</v>
       </c>
     </row>
     <row r="9">
@@ -182,13 +182,13 @@
         <v>5.5088901519775391</v>
       </c>
       <c r="C9" s="2">
-        <v>5.3203277587890625</v>
+        <v>5.3226828575134277</v>
       </c>
       <c r="D9" s="2">
         <v>5.7272243499755859</v>
       </c>
       <c r="E9" s="2">
-        <v>5.5876197814941406</v>
+        <v>5.5871663093566895</v>
       </c>
     </row>
     <row r="10">
@@ -199,13 +199,13 @@
         <v>5.08917236328125</v>
       </c>
       <c r="C10" s="2">
-        <v>4.9418225288391113</v>
+        <v>4.936708927154541</v>
       </c>
       <c r="D10" s="2">
         <v>5.7389001846313477</v>
       </c>
       <c r="E10" s="2">
-        <v>5.5812296867370605</v>
+        <v>5.5812220573425293</v>
       </c>
     </row>
     <row r="11">
@@ -216,13 +216,13 @@
         <v>6.7023992538452148</v>
       </c>
       <c r="C11" s="2">
-        <v>6.5794358253479004</v>
+        <v>6.59228515625</v>
       </c>
       <c r="D11" s="2">
         <v>5.8502249717712402</v>
       </c>
       <c r="E11" s="2">
-        <v>5.6800580024719238</v>
+        <v>5.6811833381652832</v>
       </c>
     </row>
     <row r="12">
@@ -233,13 +233,13 @@
         <v>7.1445112228393555</v>
       </c>
       <c r="C12" s="2">
-        <v>7.1960721015930176</v>
+        <v>7.1860213279724121</v>
       </c>
       <c r="D12" s="2">
         <v>6.1374540328979492</v>
       </c>
       <c r="E12" s="2">
-        <v>5.9689083099365234</v>
+        <v>5.969947338104248</v>
       </c>
     </row>
     <row r="13">
@@ -250,13 +250,13 @@
         <v>6.3416814804077148</v>
       </c>
       <c r="C13" s="2">
-        <v>5.9455466270446777</v>
+        <v>5.950523853302002</v>
       </c>
       <c r="D13" s="2">
         <v>6.369962215423584</v>
       </c>
       <c r="E13" s="2">
-        <v>6.2072410583496094</v>
+        <v>6.2098202705383301</v>
       </c>
     </row>
     <row r="14">
@@ -267,13 +267,13 @@
         <v>5.8206300735473633</v>
       </c>
       <c r="C14" s="2">
-        <v>5.5364985466003418</v>
+        <v>5.5396113395690918</v>
       </c>
       <c r="D14" s="2">
         <v>6.3614044189453125</v>
       </c>
       <c r="E14" s="2">
-        <v>6.2054867744445801</v>
+        <v>6.209172248840332</v>
       </c>
     </row>
     <row r="15">
@@ -284,13 +284,13 @@
         <v>6.7408227920532227</v>
       </c>
       <c r="C15" s="2">
-        <v>6.4706850051879883</v>
+        <v>6.4808716773986816</v>
       </c>
       <c r="D15" s="2">
         <v>6.565824031829834</v>
       </c>
       <c r="E15" s="2">
-        <v>6.4160456657409668</v>
+        <v>6.4206757545471191</v>
       </c>
     </row>
     <row r="16">
@@ -301,13 +301,13 @@
         <v>6.9616789817810059</v>
       </c>
       <c r="C16" s="2">
-        <v>6.9246959686279297</v>
+        <v>6.921295166015625</v>
       </c>
       <c r="D16" s="2">
         <v>6.5533127784729004</v>
       </c>
       <c r="E16" s="2">
-        <v>6.4030971527099609</v>
+        <v>6.4069738388061523</v>
       </c>
     </row>
     <row r="17">
@@ -318,13 +318,13 @@
         <v>7.0198736190795898</v>
       </c>
       <c r="C17" s="2">
-        <v>6.9500865936279297</v>
+        <v>6.9583830833435059</v>
       </c>
       <c r="D17" s="2">
         <v>6.4752511978149414</v>
       </c>
       <c r="E17" s="2">
-        <v>6.2902231216430664</v>
+        <v>6.2955937385559082</v>
       </c>
     </row>
     <row r="18">
@@ -335,13 +335,13 @@
         <v>5.4318685531616211</v>
       </c>
       <c r="C18" s="2">
-        <v>5.304537296295166</v>
+        <v>5.3168492317199707</v>
       </c>
       <c r="D18" s="2">
         <v>6.4657926559448242</v>
       </c>
       <c r="E18" s="2">
-        <v>6.2923417091369629</v>
+        <v>6.2974033355712891</v>
       </c>
     </row>
     <row r="19">
@@ -352,13 +352,13 @@
         <v>6.928950309753418</v>
       </c>
       <c r="C19" s="2">
-        <v>6.8368544578552246</v>
+        <v>6.8402423858642578</v>
       </c>
       <c r="D19" s="2">
         <v>6.5046501159667969</v>
       </c>
       <c r="E19" s="2">
-        <v>6.371330738067627</v>
+        <v>6.3764991760253906</v>
       </c>
     </row>
     <row r="20">
@@ -369,13 +369,13 @@
         <v>6.5897998809814453</v>
       </c>
       <c r="C20" s="2">
-        <v>6.4628968238830566</v>
+        <v>6.4689645767211914</v>
       </c>
       <c r="D20" s="2">
         <v>6.5902962684631348</v>
       </c>
       <c r="E20" s="2">
-        <v>6.460538387298584</v>
+        <v>6.4653000831604004</v>
       </c>
     </row>
     <row r="21">
@@ -386,13 +386,13 @@
         <v>6.4419560432434082</v>
       </c>
       <c r="C21" s="2">
-        <v>6.1802077293395996</v>
+        <v>6.1836013793945312</v>
       </c>
       <c r="D21" s="2">
         <v>6.5911030769348145</v>
       </c>
       <c r="E21" s="2">
-        <v>6.4641542434692383</v>
+        <v>6.470395565032959</v>
       </c>
     </row>
     <row r="22">
@@ -403,13 +403,13 @@
         <v>6.2565526962280273</v>
       </c>
       <c r="C22" s="2">
-        <v>5.9646143913269043</v>
+        <v>5.9668121337890625</v>
       </c>
       <c r="D22" s="2">
         <v>6.5778684616088867</v>
       </c>
       <c r="E22" s="2">
-        <v>6.4368319511413574</v>
+        <v>6.4423561096191406</v>
       </c>
     </row>
     <row r="23">
@@ -420,13 +420,13 @@
         <v>6.1703476905822754</v>
       </c>
       <c r="C23" s="2">
-        <v>6.2474002838134766</v>
+        <v>6.2514739036560059</v>
       </c>
       <c r="D23" s="2">
         <v>6.8175868988037109</v>
       </c>
       <c r="E23" s="2">
-        <v>6.6761946678161621</v>
+        <v>6.680384635925293</v>
       </c>
     </row>
     <row r="24">
@@ -437,13 +437,13 @@
         <v>7.5116400718688965</v>
       </c>
       <c r="C24" s="2">
-        <v>7.2735505104064941</v>
+        <v>7.2800798416137695</v>
       </c>
       <c r="D24" s="2">
         <v>6.6747927665710449</v>
       </c>
       <c r="E24" s="2">
-        <v>6.5404620170593262</v>
+        <v>6.5445156097412109</v>
       </c>
     </row>
     <row r="25">
@@ -454,13 +454,13 @@
         <v>6.9689383506774902</v>
       </c>
       <c r="C25" s="2">
-        <v>6.9572386741638184</v>
+        <v>6.9671516418457031</v>
       </c>
       <c r="D25" s="2">
         <v>6.5991482734680176</v>
       </c>
       <c r="E25" s="2">
-        <v>6.5009040832519531</v>
+        <v>6.5035934448242188</v>
       </c>
     </row>
     <row r="26">
@@ -471,13 +471,13 @@
         <v>6.9007606506347656</v>
       </c>
       <c r="C26" s="2">
-        <v>6.7041864395141602</v>
+        <v>6.7060308456420898</v>
       </c>
       <c r="D26" s="2">
         <v>6.5725560188293457</v>
       </c>
       <c r="E26" s="2">
-        <v>6.4806900024414062</v>
+        <v>6.4838447570800781</v>
       </c>
     </row>
     <row r="27">
@@ -488,13 +488,13 @@
         <v>7.5893359184265137</v>
       </c>
       <c r="C27" s="2">
-        <v>7.4588007926940918</v>
+        <v>7.4591054916381836</v>
       </c>
       <c r="D27" s="2">
         <v>6.5490598678588867</v>
       </c>
       <c r="E27" s="2">
-        <v>6.4856328964233398</v>
+        <v>6.4882106781005859</v>
       </c>
     </row>
     <row r="28">
@@ -505,13 +505,13 @@
         <v>5.6438055038452148</v>
       </c>
       <c r="C28" s="2">
-        <v>5.6152615547180176</v>
+        <v>5.6174197196960449</v>
       </c>
       <c r="D28" s="2">
         <v>6.5775609016418457</v>
       </c>
       <c r="E28" s="2">
-        <v>6.4934558868408203</v>
+        <v>6.4969143867492676</v>
       </c>
     </row>
     <row r="29">
@@ -522,13 +522,13 @@
         <v>5.9089961051940918</v>
       </c>
       <c r="C29" s="2">
-        <v>6.1068782806396484</v>
+        <v>6.1006669998168945</v>
       </c>
       <c r="D29" s="2">
         <v>6.4952526092529297</v>
       </c>
       <c r="E29" s="2">
-        <v>6.4113893508911133</v>
+        <v>6.4143438339233398</v>
       </c>
     </row>
     <row r="30">
@@ -539,13 +539,13 @@
         <v>6.2026290893554688</v>
       </c>
       <c r="C30" s="2">
-        <v>5.9982805252075195</v>
+        <v>6.0058636665344238</v>
       </c>
       <c r="D30" s="2">
         <v>6.533477783203125</v>
       </c>
       <c r="E30" s="2">
-        <v>6.4329681396484375</v>
+        <v>6.4346923828125</v>
       </c>
     </row>
     <row r="31">
@@ -556,13 +556,13 @@
         <v>6.0450873374938965</v>
       </c>
       <c r="C31" s="2">
-        <v>6.0090970993041992</v>
+        <v>6.0061030387878418</v>
       </c>
       <c r="D31" s="2">
         <v>6.4435620307922363</v>
       </c>
       <c r="E31" s="2">
-        <v>6.3634533882141113</v>
+        <v>6.3646655082702637</v>
       </c>
     </row>
     <row r="32">
@@ -573,13 +573,13 @@
         <v>6.4268560409545898</v>
       </c>
       <c r="C32" s="2">
-        <v>6.3178071975708008</v>
+        <v>6.3298091888427734</v>
       </c>
       <c r="D32" s="2">
         <v>6.2075600624084473</v>
       </c>
       <c r="E32" s="2">
-        <v>6.1469736099243164</v>
+        <v>6.1475386619567871</v>
       </c>
     </row>
     <row r="33">
@@ -590,13 +590,13 @@
         <v>6.7708635330200195</v>
       </c>
       <c r="C33" s="2">
-        <v>6.5349550247192383</v>
+        <v>6.5369420051574707</v>
       </c>
       <c r="D33" s="2">
         <v>6.1695270538330078</v>
       </c>
       <c r="E33" s="2">
-        <v>6.0938324928283691</v>
+        <v>6.0945558547973633</v>
       </c>
     </row>
     <row r="34">
@@ -607,13 +607,13 @@
         <v>7.3129644393920898</v>
       </c>
       <c r="C34" s="2">
-        <v>7.1514449119567871</v>
+        <v>7.1502890586853027</v>
       </c>
       <c r="D34" s="2">
         <v>6.1940207481384277</v>
       </c>
       <c r="E34" s="2">
-        <v>6.0881528854370117</v>
+        <v>6.0890288352966309</v>
       </c>
     </row>
     <row r="35">
@@ -624,13 +624,13 @@
         <v>6.091519832611084</v>
       </c>
       <c r="C35" s="2">
-        <v>6.0785560607910156</v>
+        <v>6.0757918357849121</v>
       </c>
       <c r="D35" s="2">
         <v>6.1752529144287109</v>
       </c>
       <c r="E35" s="2">
-        <v>6.0929131507873535</v>
+        <v>6.0938024520874023</v>
       </c>
     </row>
     <row r="36">
@@ -641,13 +641,13 @@
         <v>5.4653201103210449</v>
       </c>
       <c r="C36" s="2">
-        <v>5.5104818344116211</v>
+        <v>5.5049624443054199</v>
       </c>
       <c r="D36" s="2">
         <v>6.1984052658081055</v>
       </c>
       <c r="E36" s="2">
-        <v>6.1134676933288574</v>
+        <v>6.115656852722168</v>
       </c>
     </row>
     <row r="37">
@@ -658,13 +658,13 @@
         <v>5.301506519317627</v>
       </c>
       <c r="C37" s="2">
-        <v>5.136991024017334</v>
+        <v>5.1405758857727051</v>
       </c>
       <c r="D37" s="2">
         <v>6.1795182228088379</v>
       </c>
       <c r="E37" s="2">
-        <v>6.0851140022277832</v>
+        <v>6.0852055549621582</v>
       </c>
     </row>
     <row r="38">
@@ -675,13 +675,13 @@
         <v>6.1294403076171875</v>
       </c>
       <c r="C38" s="2">
-        <v>6.0557632446289062</v>
+        <v>6.0509238243103027</v>
       </c>
       <c r="D38" s="2">
         <v>6.1320891380310059</v>
       </c>
       <c r="E38" s="2">
-        <v>6.0503578186035156</v>
+        <v>6.0499801635742188</v>
       </c>
     </row>
     <row r="39">
@@ -692,13 +692,13 @@
         <v>6.0337200164794922</v>
       </c>
       <c r="C39" s="2">
-        <v>6.0411200523376465</v>
+        <v>6.0488266944885254</v>
       </c>
       <c r="D39" s="2">
         <v>5.9034738540649414</v>
       </c>
       <c r="E39" s="2">
-        <v>5.8029265403747559</v>
+        <v>5.8038821220397949</v>
       </c>
     </row>
     <row r="40">
@@ -709,13 +709,13 @@
         <v>6.2534551620483398</v>
       </c>
       <c r="C40" s="2">
-        <v>6.1940889358520508</v>
+        <v>6.2027902603149414</v>
       </c>
       <c r="D40" s="2">
         <v>5.9057126045227051</v>
       </c>
       <c r="E40" s="2">
-        <v>5.7815051078796387</v>
+        <v>5.782872200012207</v>
       </c>
     </row>
     <row r="41">
@@ -726,13 +726,13 @@
         <v>6.2568740844726562</v>
       </c>
       <c r="C41" s="2">
-        <v>6.0626249313354492</v>
+        <v>6.0557489395141602</v>
       </c>
       <c r="D41" s="2">
         <v>6.0877313613891602</v>
       </c>
       <c r="E41" s="2">
-        <v>5.9359631538391113</v>
+        <v>5.9390082359313965</v>
       </c>
     </row>
     <row r="42">
@@ -743,13 +743,13 @@
         <v>6.3440008163452148</v>
       </c>
       <c r="C42" s="2">
-        <v>6.2221479415893555</v>
+        <v>6.2199110984802246</v>
       </c>
       <c r="D42" s="2">
         <v>6.1198782920837402</v>
       </c>
       <c r="E42" s="2">
-        <v>5.9861273765563965</v>
+        <v>5.9887518882751465</v>
       </c>
     </row>
     <row r="43">
@@ -760,13 +760,13 @@
         <v>5.2554292678833008</v>
       </c>
       <c r="C43" s="2">
-        <v>4.9245648384094238</v>
+        <v>4.9354081153869629</v>
       </c>
       <c r="D43" s="2">
         <v>6.0441641807556152</v>
       </c>
       <c r="E43" s="2">
-        <v>5.9147405624389648</v>
+        <v>5.9173417091369629</v>
       </c>
     </row>
     <row r="44">
@@ -777,13 +777,13 @@
         <v>6.1116690635681152</v>
       </c>
       <c r="C44" s="2">
-        <v>5.8857650756835938</v>
+        <v>5.8867034912109375</v>
       </c>
       <c r="D44" s="2">
         <v>6.055727481842041</v>
       </c>
       <c r="E44" s="2">
-        <v>5.8957853317260742</v>
+        <v>5.896334171295166</v>
       </c>
     </row>
     <row r="45">
@@ -794,13 +794,13 @@
         <v>7.1034855842590332</v>
       </c>
       <c r="C45" s="2">
-        <v>6.9006037712097168</v>
+        <v>6.9101853370666504</v>
       </c>
       <c r="D45" s="2">
         <v>6.1613049507141113</v>
       </c>
       <c r="E45" s="2">
-        <v>6.0151910781860352</v>
+        <v>6.0140047073364258</v>
       </c>
     </row>
     <row r="46">
@@ -811,13 +811,13 @@
         <v>5.5908308029174805</v>
       </c>
       <c r="C46" s="2">
-        <v>5.588465690612793</v>
+        <v>5.5882678031921387</v>
       </c>
       <c r="D46" s="2">
         <v>6.293513298034668</v>
       </c>
       <c r="E46" s="2">
-        <v>6.1771855354309082</v>
+        <v>6.1758589744567871</v>
       </c>
     </row>
     <row r="47">
@@ -828,13 +828,13 @@
         <v>5.4480128288269043</v>
       </c>
       <c r="C47" s="2">
-        <v>5.4132843017578125</v>
+        <v>5.4082341194152832</v>
       </c>
       <c r="D47" s="2">
         <v>6.3882975578308105</v>
       </c>
       <c r="E47" s="2">
-        <v>6.299750804901123</v>
+        <v>6.298499584197998</v>
       </c>
     </row>
     <row r="48">
@@ -845,13 +845,13 @@
         <v>6.1377911567687988</v>
       </c>
       <c r="C48" s="2">
-        <v>5.8705215454101562</v>
+        <v>5.8597583770751953</v>
       </c>
       <c r="D48" s="2">
         <v>6.5736865997314453</v>
       </c>
       <c r="E48" s="2">
-        <v>6.5246491432189941</v>
+        <v>6.5222129821777344</v>
       </c>
     </row>
     <row r="49">
@@ -862,13 +862,13 @@
         <v>7.2036523818969727</v>
       </c>
       <c r="C49" s="2">
-        <v>7.2687416076660156</v>
+        <v>7.2618255615234375</v>
       </c>
       <c r="D49" s="2">
         <v>6.615668773651123</v>
       </c>
       <c r="E49" s="2">
-        <v>6.5841388702392578</v>
+        <v>6.5809588432312012</v>
       </c>
     </row>
     <row r="50">
@@ -879,13 +879,13 @@
         <v>7.4467463493347168</v>
       </c>
       <c r="C50" s="2">
-        <v>7.520576000213623</v>
+        <v>7.5124354362487793</v>
       </c>
       <c r="D50" s="2">
         <v>6.4916987419128418</v>
       </c>
       <c r="E50" s="2">
-        <v>6.4692201614379883</v>
+        <v>6.4652342796325684</v>
       </c>
     </row>
     <row r="51">
@@ -896,13 +896,13 @@
         <v>7.1970605850219727</v>
       </c>
       <c r="C51" s="2">
-        <v>7.3252363204956055</v>
+        <v>7.323676586151123</v>
       </c>
       <c r="D51" s="2">
         <v>6.6447196006774902</v>
       </c>
       <c r="E51" s="2">
-        <v>6.6297731399536133</v>
+        <v>6.6258625984191895</v>
       </c>
     </row>
     <row r="52">
@@ -913,13 +913,13 @@
         <v>6.9239311218261719</v>
       </c>
       <c r="C52" s="2">
-        <v>6.9486470222473145</v>
+        <v>6.948829174041748</v>
       </c>
       <c r="D52" s="2">
         <v>6.7505278587341309</v>
       </c>
       <c r="E52" s="2">
-        <v>6.7215428352355957</v>
+        <v>6.7195582389831543</v>
       </c>
     </row>
     <row r="53">
@@ -930,13 +930,13 @@
         <v>6.489506721496582</v>
       </c>
       <c r="C53" s="2">
-        <v>6.4211726188659668</v>
+        <v>6.4154176712036133</v>
       </c>
       <c r="D53" s="2">
         <v>6.754941463470459</v>
       </c>
       <c r="E53" s="2">
-        <v>6.7535390853881836</v>
+        <v>6.7529335021972656</v>
       </c>
     </row>
     <row r="54">
@@ -947,13 +947,13 @@
         <v>5.9877557754516602</v>
       </c>
       <c r="C54" s="2">
-        <v>5.8663368225097656</v>
+        <v>5.8686656951904297</v>
       </c>
       <c r="D54" s="2">
         <v>6.6327285766601562</v>
       </c>
       <c r="E54" s="2">
-        <v>6.6066207885742188</v>
+        <v>6.6079163551330566</v>
       </c>
     </row>
     <row r="55">
@@ -964,13 +964,13 @@
         <v>6.9680194854736328</v>
       </c>
       <c r="C55" s="2">
-        <v>7.0334405899047852</v>
+        <v>7.0339212417602539</v>
       </c>
       <c r="D55" s="2">
         <v>6.5913233757019043</v>
       </c>
       <c r="E55" s="2">
-        <v>6.570427417755127</v>
+        <v>6.5722928047180176</v>
       </c>
     </row>
     <row r="56">
@@ -981,13 +981,13 @@
         <v>6.4002885818481445</v>
       </c>
       <c r="C56" s="2">
-        <v>6.2392144203186035</v>
+        <v>6.251492977142334</v>
       </c>
       <c r="D56" s="2">
         <v>6.5557041168212891</v>
       </c>
       <c r="E56" s="2">
-        <v>6.5177769660949707</v>
+        <v>6.5194792747497559</v>
       </c>
     </row>
     <row r="57">
@@ -998,13 +998,13 @@
         <v>6.1775131225585938</v>
       </c>
       <c r="C57" s="2">
-        <v>6.158484935760498</v>
+        <v>6.1601357460021973</v>
       </c>
       <c r="D57" s="2">
         <v>6.4121708869934082</v>
       </c>
       <c r="E57" s="2">
-        <v>6.3616480827331543</v>
+        <v>6.3633232116699219</v>
       </c>
     </row>
     <row r="58">
@@ -1015,13 +1015,13 @@
         <v>6.1037335395812988</v>
       </c>
       <c r="C58" s="2">
-        <v>5.9464764595031738</v>
+        <v>5.9566731452941895</v>
       </c>
       <c r="D58" s="2">
         <v>6.442194938659668</v>
       </c>
       <c r="E58" s="2">
-        <v>6.4028778076171875</v>
+        <v>6.4048504829406738</v>
       </c>
     </row>
     <row r="59">
@@ -1032,13 +1032,13 @@
         <v>7.0741024017333984</v>
       </c>
       <c r="C59" s="2">
-        <v>7.1948356628417969</v>
+        <v>7.1918230056762695</v>
       </c>
       <c r="D59" s="2">
         <v>6.434420108795166</v>
       </c>
       <c r="E59" s="2">
-        <v>6.3876934051513672</v>
+        <v>6.3886675834655762</v>
       </c>
     </row>
     <row r="60">
@@ -1049,13 +1049,13 @@
         <v>6.8764848709106445</v>
       </c>
       <c r="C60" s="2">
-        <v>6.8513855934143066</v>
+        <v>6.8483548164367676</v>
       </c>
       <c r="D60" s="2">
         <v>6.3491740226745605</v>
       </c>
       <c r="E60" s="2">
-        <v>6.2898039817810059</v>
+        <v>6.2907285690307617</v>
       </c>
     </row>
     <row r="61">
@@ -1066,13 +1066,13 @@
         <v>5.6321353912353516</v>
       </c>
       <c r="C61" s="2">
-        <v>5.5434861183166504</v>
+        <v>5.5434236526489258</v>
       </c>
       <c r="D61" s="2">
         <v>6.3328986167907715</v>
       </c>
       <c r="E61" s="2">
-        <v>6.2674093246459961</v>
+        <v>6.2669720649719238</v>
       </c>
     </row>
     <row r="62">
@@ -1083,13 +1083,13 @@
         <v>6.7597222328186035</v>
       </c>
       <c r="C62" s="2">
-        <v>6.7922382354736328</v>
+        <v>6.7891650199890137</v>
       </c>
       <c r="D62" s="2">
         <v>6.4095625877380371</v>
       </c>
       <c r="E62" s="2">
-        <v>6.3327407836914062</v>
+        <v>6.3321752548217773</v>
       </c>
     </row>
     <row r="63">
@@ -1100,13 +1100,13 @@
         <v>5.9177823066711426</v>
       </c>
       <c r="C63" s="2">
-        <v>5.7296781539916992</v>
+        <v>5.7230191230773926</v>
       </c>
       <c r="D63" s="2">
         <v>6.3646349906921387</v>
       </c>
       <c r="E63" s="2">
-        <v>6.2861127853393555</v>
+        <v>6.2844934463500977</v>
       </c>
     </row>
     <row r="64">
@@ -1117,13 +1117,13 @@
         <v>6.2008047103881836</v>
       </c>
       <c r="C64" s="2">
-        <v>6.1524357795715332</v>
+        <v>6.1524715423583984</v>
       </c>
       <c r="D64" s="2">
         <v>6.2863035202026367</v>
       </c>
       <c r="E64" s="2">
-        <v>6.1764340400695801</v>
+        <v>6.1747522354125977</v>
       </c>
     </row>
     <row r="65">
@@ -1134,13 +1134,13 @@
         <v>6.2538094520568848</v>
       </c>
       <c r="C65" s="2">
-        <v>6.0376644134521484</v>
+        <v>6.037682056427002</v>
       </c>
       <c r="D65" s="2">
         <v>6.2225532531738281</v>
       </c>
       <c r="E65" s="2">
-        <v>6.0979981422424316</v>
+        <v>6.0970163345336914</v>
       </c>
     </row>
     <row r="66">
@@ -1151,13 +1151,13 @@
         <v>6.8674893379211426</v>
       </c>
       <c r="C66" s="2">
-        <v>6.7464656829833984</v>
+        <v>6.7469649314880371</v>
       </c>
       <c r="D66" s="2">
         <v>6.2243313789367676</v>
       </c>
       <c r="E66" s="2">
-        <v>6.1026697158813477</v>
+        <v>6.1016192436218262</v>
       </c>
     </row>
     <row r="67">
@@ -1168,13 +1168,13 @@
         <v>5.6993837356567383</v>
       </c>
       <c r="C67" s="2">
-        <v>5.5268244743347168</v>
+        <v>5.5275378227233887</v>
       </c>
       <c r="D67" s="2">
         <v>6.0078926086425781</v>
       </c>
       <c r="E67" s="2">
-        <v>5.881828784942627</v>
+        <v>5.8807687759399414</v>
       </c>
     </row>
     <row r="68">
@@ -1185,13 +1185,13 @@
         <v>6.3691182136535645</v>
       </c>
       <c r="C68" s="2">
-        <v>6.2077264785766602</v>
+        <v>6.2041525840759277</v>
       </c>
       <c r="D68" s="2">
         <v>5.9613947868347168</v>
       </c>
       <c r="E68" s="2">
-        <v>5.8407011032104492</v>
+        <v>5.8398690223693848</v>
       </c>
     </row>
     <row r="69">
@@ -1202,13 +1202,13 @@
         <v>6.3027334213256836</v>
       </c>
       <c r="C69" s="2">
-        <v>6.1454644203186035</v>
+        <v>6.1487307548522949</v>
       </c>
       <c r="D69" s="2">
         <v>5.8975124359130859</v>
       </c>
       <c r="E69" s="2">
-        <v>5.7838077545166016</v>
+        <v>5.7823519706726074</v>
       </c>
     </row>
     <row r="70">
@@ -1219,13 +1219,13 @@
         <v>5.6481375694274902</v>
       </c>
       <c r="C70" s="2">
-        <v>5.5855298042297363</v>
+        <v>5.5848479270935059</v>
       </c>
       <c r="D70" s="2">
         <v>5.9526658058166504</v>
       </c>
       <c r="E70" s="2">
-        <v>5.8514113426208496</v>
+        <v>5.8493542671203613</v>
       </c>
     </row>
     <row r="71">
@@ -1236,13 +1236,13 @@
         <v>4.8117733001708984</v>
       </c>
       <c r="C71" s="2">
-        <v>4.8046679496765137</v>
+        <v>4.8015122413635254</v>
       </c>
       <c r="D71" s="2">
         <v>5.9479408264160156</v>
       </c>
       <c r="E71" s="2">
-        <v>5.8746509552001953</v>
+        <v>5.8712024688720703</v>
       </c>
     </row>
     <row r="72">
@@ -1253,13 +1253,13 @@
         <v>5.4993038177490234</v>
       </c>
       <c r="C72" s="2">
-        <v>5.3595290184020996</v>
+        <v>5.3549213409423828</v>
       </c>
       <c r="D72" s="2">
         <v>5.9946599006652832</v>
       </c>
       <c r="E72" s="2">
-        <v>5.9178066253662109</v>
+        <v>5.9155430793762207</v>
       </c>
     </row>
     <row r="73">
@@ -1270,13 +1270,13 @@
         <v>5.6258621215820312</v>
       </c>
       <c r="C73" s="2">
-        <v>5.6403980255126953</v>
+        <v>5.6348176002502441</v>
       </c>
       <c r="D73" s="2">
         <v>6.0496644973754883</v>
       </c>
       <c r="E73" s="2">
-        <v>5.9932827949523926</v>
+        <v>5.9914445877075195</v>
       </c>
     </row>
     <row r="74">
@@ -1287,13 +1287,13 @@
         <v>6.7501888275146484</v>
       </c>
       <c r="C74" s="2">
-        <v>6.6460967063903809</v>
+        <v>6.6407012939453125</v>
       </c>
       <c r="D74" s="2">
         <v>6.0850920677185059</v>
       </c>
       <c r="E74" s="2">
-        <v>6.0543923377990723</v>
+        <v>6.051694393157959</v>
       </c>
     </row>
     <row r="75">
@@ -1304,13 +1304,13 @@
         <v>6.8249673843383789</v>
       </c>
       <c r="C75" s="2">
-        <v>6.955620288848877</v>
+        <v>6.9435992240905762</v>
       </c>
       <c r="D75" s="2">
         <v>6.1572055816650391</v>
       </c>
       <c r="E75" s="2">
-        <v>6.1262078285217285</v>
+        <v>6.1233420372009277</v>
       </c>
     </row>
     <row r="76">
@@ -1321,13 +1321,13 @@
         <v>6.1198534965515137</v>
       </c>
       <c r="C76" s="2">
-        <v>5.9152288436889648</v>
+        <v>5.9266033172607422</v>
       </c>
       <c r="D76" s="2">
         <v>6.3904237747192383</v>
       </c>
       <c r="E76" s="2">
-        <v>6.3390092849731445</v>
+        <v>6.336876392364502</v>
       </c>
     </row>
     <row r="77">
@@ -1338,13 +1338,13 @@
         <v>6.864161491394043</v>
       </c>
       <c r="C77" s="2">
-        <v>6.8870081901550293</v>
+        <v>6.8872685432434082</v>
       </c>
       <c r="D77" s="2">
         <v>6.4813189506530762</v>
       </c>
       <c r="E77" s="2">
-        <v>6.434168815612793</v>
+        <v>6.4321165084838867</v>
       </c>
     </row>
     <row r="78">
@@ -1355,13 +1355,13 @@
         <v>6.6215806007385254</v>
       </c>
       <c r="C78" s="2">
-        <v>6.6954512596130371</v>
+        <v>6.6909775733947754</v>
       </c>
       <c r="D78" s="2">
         <v>6.6365394592285156</v>
       </c>
       <c r="E78" s="2">
-        <v>6.5702166557312012</v>
+        <v>6.5684366226196289</v>
       </c>
     </row>
     <row r="79">
@@ -1372,13 +1372,13 @@
         <v>6.2971606254577637</v>
       </c>
       <c r="C79" s="2">
-        <v>6.2318692207336426</v>
+        <v>6.22967529296875</v>
       </c>
       <c r="D79" s="2">
         <v>6.6221461296081543</v>
       </c>
       <c r="E79" s="2">
-        <v>6.5312328338623047</v>
+        <v>6.5301337242126465</v>
       </c>
     </row>
     <row r="80">
@@ -1389,13 +1389,13 @@
         <v>6.9107375144958496</v>
       </c>
       <c r="C80" s="2">
-        <v>6.7198829650878906</v>
+        <v>6.7233242988586426</v>
       </c>
       <c r="D80" s="2">
         <v>6.5040831565856934</v>
       </c>
       <c r="E80" s="2">
-        <v>6.3711495399475098</v>
+        <v>6.3708906173706055</v>
       </c>
     </row>
     <row r="81">
@@ -1406,13 +1406,13 @@
         <v>6.3173575401306152</v>
       </c>
       <c r="C81" s="2">
-        <v>6.2159619331359863</v>
+        <v>6.2120819091796875</v>
       </c>
       <c r="D81" s="2">
         <v>6.549626350402832</v>
       </c>
       <c r="E81" s="2">
-        <v>6.4003543853759766</v>
+        <v>6.4003238677978516</v>
       </c>
     </row>
     <row r="82">
@@ -1423,13 +1423,13 @@
         <v>7.0228486061096191</v>
       </c>
       <c r="C82" s="2">
-        <v>6.8648295402526855</v>
+        <v>6.8616971969604492</v>
       </c>
       <c r="D82" s="2">
         <v>6.398247241973877</v>
       </c>
       <c r="E82" s="2">
-        <v>6.2502241134643555</v>
+        <v>6.2494759559631348</v>
       </c>
     </row>
     <row r="83">
@@ -1440,13 +1440,13 @@
         <v>6.6206493377685547</v>
       </c>
       <c r="C83" s="2">
-        <v>6.2952432632446289</v>
+        <v>6.2959780693054199</v>
       </c>
       <c r="D83" s="2">
         <v>6.3949055671691895</v>
       </c>
       <c r="E83" s="2">
-        <v>6.2341513633728027</v>
+        <v>6.234036922454834</v>
       </c>
     </row>
     <row r="84">
@@ -1457,13 +1457,13 @@
         <v>5.7624011039733887</v>
       </c>
       <c r="C84" s="2">
-        <v>5.5148711204528809</v>
+        <v>5.510411262512207</v>
       </c>
       <c r="D84" s="2">
         <v>6.4814581871032715</v>
       </c>
       <c r="E84" s="2">
-        <v>6.3315620422363281</v>
+        <v>6.3310604095458984</v>
       </c>
     </row>
     <row r="85">
@@ -1474,13 +1474,13 @@
         <v>6.5297408103942871</v>
       </c>
       <c r="C85" s="2">
-        <v>6.1780705451965332</v>
+        <v>6.1915006637573242</v>
       </c>
       <c r="D85" s="2">
         <v>6.6420841217041016</v>
       </c>
       <c r="E85" s="2">
-        <v>6.4826135635375977</v>
+        <v>6.4823212623596191</v>
       </c>
     </row>
     <row r="86">
@@ -1491,13 +1491,13 @@
         <v>5.5017471313476562</v>
       </c>
       <c r="C86" s="2">
-        <v>5.5358366966247559</v>
+        <v>5.5296378135681152</v>
       </c>
       <c r="D86" s="2">
         <v>6.8498764038085938</v>
       </c>
       <c r="E86" s="2">
-        <v>6.6846060752868652</v>
+        <v>6.6848382949829102</v>
       </c>
     </row>
     <row r="87">
@@ -1508,13 +1508,13 @@
         <v>6.5915093421936035</v>
       </c>
       <c r="C87" s="2">
-        <v>6.5507960319519043</v>
+        <v>6.5520257949829102</v>
       </c>
       <c r="D87" s="2">
         <v>6.8130464553833008</v>
       </c>
       <c r="E87" s="2">
-        <v>6.6299853324890137</v>
+        <v>6.6312723159790039</v>
       </c>
     </row>
     <row r="88">
@@ -1525,13 +1525,13 @@
         <v>7.076134204864502</v>
       </c>
       <c r="C88" s="2">
-        <v>7.1085643768310547</v>
+        <v>7.1028852462768555</v>
       </c>
       <c r="D88" s="2">
         <v>6.9035587310791016</v>
       </c>
       <c r="E88" s="2">
-        <v>6.7483086585998535</v>
+        <v>6.7492833137512207</v>
       </c>
     </row>
     <row r="89">
@@ -1542,13 +1542,13 @@
         <v>8.3563680648803711</v>
       </c>
       <c r="C89" s="2">
-        <v>8.0793466567993164</v>
+        <v>8.0846719741821289</v>
       </c>
       <c r="D89" s="2">
         <v>7.0460209846496582</v>
       </c>
       <c r="E89" s="2">
-        <v>6.8978948593139648</v>
+        <v>6.8992676734924316</v>
       </c>
     </row>
     <row r="90">
@@ -1559,13 +1559,13 @@
         <v>8.1874904632568359</v>
       </c>
       <c r="C90" s="2">
-        <v>8.0338945388793945</v>
+        <v>8.0347366333007812</v>
       </c>
       <c r="D90" s="2">
         <v>7.046541690826416</v>
       </c>
       <c r="E90" s="2">
-        <v>6.9241905212402344</v>
+        <v>6.9249734878540039</v>
       </c>
     </row>
     <row r="91">
@@ -1576,13 +1576,13 @@
         <v>6.6913776397705078</v>
       </c>
       <c r="C91" s="2">
-        <v>6.3732461929321289</v>
+        <v>6.3796024322509766</v>
       </c>
       <c r="D91" s="2">
         <v>7.2546029090881348</v>
       </c>
       <c r="E91" s="2">
-        <v>7.0974197387695312</v>
+        <v>7.098731517791748</v>
       </c>
     </row>
     <row r="92">
@@ -1593,13 +1593,13 @@
         <v>7.4352602958679199</v>
       </c>
       <c r="C92" s="2">
-        <v>7.3601517677307129</v>
+        <v>7.3580770492553711</v>
       </c>
       <c r="D92" s="2">
         <v>7.1930127143859863</v>
       </c>
       <c r="E92" s="2">
-        <v>7.0443248748779297</v>
+        <v>7.0459699630737305</v>
       </c>
     </row>
     <row r="93">
@@ -1610,13 +1610,13 @@
         <v>7.0445599555969238</v>
       </c>
       <c r="C93" s="2">
-        <v>6.8611454963684082</v>
+        <v>6.8602719306945801</v>
       </c>
       <c r="D93" s="2">
         <v>7.2433185577392578</v>
       </c>
       <c r="E93" s="2">
-        <v>7.0899596214294434</v>
+        <v>7.0933389663696289</v>
       </c>
     </row>
     <row r="94">
@@ -1627,13 +1627,13 @@
         <v>6.5344271659851074</v>
       </c>
       <c r="C94" s="2">
-        <v>6.41473388671875</v>
+        <v>6.4228506088256836</v>
       </c>
       <c r="D94" s="2">
         <v>7.1680703163146973</v>
       </c>
       <c r="E94" s="2">
-        <v>7.0378818511962891</v>
+        <v>7.0414385795593262</v>
       </c>
     </row>
     <row r="95">
@@ -1644,13 +1644,13 @@
         <v>7.3743009567260742</v>
       </c>
       <c r="C95" s="2">
-        <v>7.0948977470397949</v>
+        <v>7.0934610366821289</v>
       </c>
       <c r="D95" s="2">
         <v>6.9110846519470215</v>
       </c>
       <c r="E95" s="2">
-        <v>6.7939324378967285</v>
+        <v>6.7960190773010254</v>
       </c>
     </row>
     <row r="96">
@@ -1661,13 +1661,13 @@
         <v>6.0371966361999512</v>
       </c>
       <c r="C96" s="2">
-        <v>6.072941780090332</v>
+        <v>6.077174186706543</v>
       </c>
       <c r="D96" s="2">
         <v>6.8539166450500488</v>
       </c>
       <c r="E96" s="2">
-        <v>6.7688422203063965</v>
+        <v>6.770230770111084</v>
       </c>
     </row>
     <row r="97">
@@ -1678,13 +1678,13 @@
         <v>7.5288867950439453</v>
       </c>
       <c r="C97" s="2">
-        <v>7.5192766189575195</v>
+        <v>7.5292043685913086</v>
       </c>
       <c r="D97" s="2">
         <v>6.7651395797729492</v>
       </c>
       <c r="E97" s="2">
-        <v>6.6680588722229004</v>
+        <v>6.6697883605957031</v>
       </c>
     </row>
     <row r="98">
@@ -1695,13 +1695,13 @@
         <v>7.6791324615478516</v>
       </c>
       <c r="C98" s="2">
-        <v>7.6106481552124023</v>
+        <v>7.6175680160522461</v>
       </c>
       <c r="D98" s="2">
         <v>6.5980830192565918</v>
       </c>
       <c r="E98" s="2">
-        <v>6.4983177185058594</v>
+        <v>6.499631404876709</v>
       </c>
     </row>
     <row r="99">
@@ -1712,13 +1712,13 @@
         <v>5.8746209144592285</v>
       </c>
       <c r="C99" s="2">
-        <v>5.8383512496948242</v>
+        <v>5.825960636138916</v>
       </c>
       <c r="D99" s="2">
         <v>6.5619583129882812</v>
       </c>
       <c r="E99" s="2">
-        <v>6.4651222229003906</v>
+        <v>6.4667692184448242</v>
       </c>
     </row>
     <row r="100">
@@ -1729,13 +1729,13 @@
         <v>6.1768641471862793</v>
       </c>
       <c r="C100" s="2">
-        <v>6.1474318504333496</v>
+        <v>6.1475095748901367</v>
       </c>
       <c r="D100" s="2">
         <v>6.5209565162658691</v>
       </c>
       <c r="E100" s="2">
-        <v>6.4486913681030273</v>
+        <v>6.4493522644042969</v>
       </c>
     </row>
     <row r="101">
@@ -1746,13 +1746,13 @@
         <v>6.6362686157226562</v>
       </c>
       <c r="C101" s="2">
-        <v>6.4531035423278809</v>
+        <v>6.454096794128418</v>
       </c>
       <c r="D101" s="2">
         <v>6.5136809349060059</v>
       </c>
       <c r="E101" s="2">
-        <v>6.4330120086669922</v>
+        <v>6.4323701858520508</v>
       </c>
     </row>
     <row r="102">
@@ -1763,13 +1763,13 @@
         <v>5.5410513877868652</v>
       </c>
       <c r="C102" s="2">
-        <v>5.3334736824035645</v>
+        <v>5.3288593292236328</v>
       </c>
       <c r="D102" s="2">
         <v>6.3885221481323242</v>
       </c>
       <c r="E102" s="2">
-        <v>6.2881875038146973</v>
+        <v>6.286470890045166</v>
       </c>
     </row>
     <row r="103">
@@ -1780,13 +1780,13 @@
         <v>6.2093029022216797</v>
       </c>
       <c r="C103" s="2">
-        <v>6.1159772872924805</v>
+        <v>6.1270890235900879</v>
       </c>
       <c r="D103" s="2">
         <v>6.1262545585632324</v>
       </c>
       <c r="E103" s="2">
-        <v>6.021721363067627</v>
+        <v>6.0191736221313477</v>
       </c>
     </row>
     <row r="104">
@@ -1797,13 +1797,13 @@
         <v>7.0052847862243652</v>
       </c>
       <c r="C104" s="2">
-        <v>6.9470171928405762</v>
+        <v>6.9367084503173828</v>
       </c>
       <c r="D104" s="2">
         <v>6.1156749725341797</v>
       </c>
       <c r="E104" s="2">
-        <v>6.0179662704467773</v>
+        <v>6.0157346725463867</v>
       </c>
     </row>
     <row r="105">
@@ -1814,13 +1814,13 @@
         <v>5.9717144966125488</v>
       </c>
       <c r="C105" s="2">
-        <v>5.9318294525146484</v>
+        <v>5.9243369102478027</v>
       </c>
       <c r="D105" s="2">
         <v>6.0591340065002441</v>
       </c>
       <c r="E105" s="2">
-        <v>5.9635748863220215</v>
+        <v>5.9624309539794922</v>
       </c>
     </row>
     <row r="106">
@@ -1831,13 +1831,13 @@
         <v>6.4024615287780762</v>
       </c>
       <c r="C106" s="2">
-        <v>6.215855598449707</v>
+        <v>6.2161083221435547</v>
       </c>
       <c r="D106" s="2">
         <v>5.9271655082702637</v>
       </c>
       <c r="E106" s="2">
-        <v>5.8261380195617676</v>
+        <v>5.8255629539489746</v>
       </c>
     </row>
     <row r="107">
@@ -1848,13 +1848,13 @@
         <v>5.318723201751709</v>
       </c>
       <c r="C107" s="2">
-        <v>5.2124509811401367</v>
+        <v>5.2118935585021973</v>
       </c>
       <c r="D107" s="2">
         <v>5.8447022438049316</v>
       </c>
       <c r="E107" s="2">
-        <v>5.7283716201782227</v>
+        <v>5.7292838096618652</v>
       </c>
     </row>
     <row r="108">
@@ -1865,13 +1865,13 @@
         <v>5.7794046401977539</v>
       </c>
       <c r="C108" s="2">
-        <v>5.8045568466186523</v>
+        <v>5.7950091361999512</v>
       </c>
       <c r="D108" s="2">
         <v>5.8590126037597656</v>
       </c>
       <c r="E108" s="2">
-        <v>5.728212833404541</v>
+        <v>5.7284879684448242</v>
       </c>
     </row>
     <row r="109">
@@ -1882,13 +1882,13 @@
         <v>5.6679949760437012</v>
       </c>
       <c r="C109" s="2">
-        <v>5.6579079627990723</v>
+        <v>5.6677765846252441</v>
       </c>
       <c r="D109" s="2">
         <v>5.7989025115966797</v>
       </c>
       <c r="E109" s="2">
-        <v>5.6813201904296875</v>
+        <v>5.6836166381835938</v>
       </c>
     </row>
     <row r="110">
@@ -1899,13 +1899,13 @@
         <v>5.4485507011413574</v>
       </c>
       <c r="C110" s="2">
-        <v>5.2161722183227539</v>
+        <v>5.2222862243652344</v>
       </c>
       <c r="D110" s="2">
         <v>5.830256462097168</v>
       </c>
       <c r="E110" s="2">
-        <v>5.6947383880615234</v>
+        <v>5.6975874900817871</v>
       </c>
     </row>
     <row r="111">
@@ -1916,13 +1916,13 @@
         <v>4.7988824844360352</v>
       </c>
       <c r="C111" s="2">
-        <v>4.4535760879516602</v>
+        <v>4.4623479843139648</v>
       </c>
       <c r="D111" s="2">
         <v>5.9050545692443848</v>
       </c>
       <c r="E111" s="2">
-        <v>5.7559785842895508</v>
+        <v>5.7590823173522949</v>
       </c>
     </row>
     <row r="112">
@@ -1933,13 +1933,13 @@
         <v>6.3380980491638184</v>
       </c>
       <c r="C112" s="2">
-        <v>6.1145510673522949</v>
+        <v>6.1199235916137695</v>
       </c>
       <c r="D112" s="2">
         <v>6.2336416244506836</v>
       </c>
       <c r="E112" s="2">
-        <v>6.0842127799987793</v>
+        <v>6.0870847702026367</v>
       </c>
     </row>
     <row r="113">
@@ -1950,13 +1950,13 @@
         <v>6.4642910957336426</v>
       </c>
       <c r="C113" s="2">
-        <v>6.5249814987182617</v>
+        <v>6.5328664779663086</v>
       </c>
       <c r="D113" s="2">
         <v>6.464024543762207</v>
       </c>
       <c r="E113" s="2">
-        <v>6.2937068939208984</v>
+        <v>6.2984657287597656</v>
       </c>
     </row>
     <row r="114">
@@ -1967,13 +1967,13 @@
         <v>6.2539033889770508</v>
       </c>
       <c r="C114" s="2">
-        <v>6.0525922775268555</v>
+        <v>6.0500764846801758</v>
       </c>
       <c r="D114" s="2">
         <v>6.4126667976379395</v>
       </c>
       <c r="E114" s="2">
-        <v>6.2615141868591309</v>
+        <v>6.2630853652954102</v>
       </c>
     </row>
     <row r="115">
@@ -1984,13 +1984,13 @@
         <v>7.0756411552429199</v>
       </c>
       <c r="C115" s="2">
-        <v>6.7670178413391113</v>
+        <v>6.7695608139038086</v>
       </c>
       <c r="D115" s="2">
         <v>6.4821228981018066</v>
       </c>
       <c r="E115" s="2">
-        <v>6.3014016151428223</v>
+        <v>6.3024172782897949</v>
       </c>
     </row>
     <row r="116">
@@ -2001,13 +2001,13 @@
         <v>8.2760095596313477</v>
       </c>
       <c r="C116" s="2">
-        <v>8.1665582656860352</v>
+        <v>8.1639137268066406</v>
       </c>
       <c r="D116" s="2">
         <v>6.6441183090209961</v>
       </c>
       <c r="E116" s="2">
-        <v>6.4833931922912598</v>
+        <v>6.4834094047546387</v>
       </c>
     </row>
     <row r="117">
@@ -2018,13 +2018,13 @@
         <v>7.8528504371643066</v>
       </c>
       <c r="C117" s="2">
-        <v>7.690004825592041</v>
+        <v>7.6974396705627441</v>
       </c>
       <c r="D117" s="2">
         <v>6.5947327613830566</v>
       </c>
       <c r="E117" s="2">
-        <v>6.4187512397766113</v>
+        <v>6.4189105033874512</v>
       </c>
     </row>
     <row r="118">
@@ -2035,13 +2035,13 @@
         <v>5.2057738304138184</v>
       </c>
       <c r="C118" s="2">
-        <v>5.3681745529174805</v>
+        <v>5.3493514060974121</v>
       </c>
       <c r="D118" s="2">
         <v>6.8340396881103516</v>
       </c>
       <c r="E118" s="2">
-        <v>6.6337847709655762</v>
+        <v>6.6334443092346191</v>
       </c>
     </row>
     <row r="119">
@@ -2052,13 +2052,13 @@
         <v>6.0736546516418457</v>
       </c>
       <c r="C119" s="2">
-        <v>5.5751595497131348</v>
+        <v>5.5762758255004883</v>
       </c>
       <c r="D119" s="2">
         <v>6.8994770050048828</v>
       </c>
       <c r="E119" s="2">
-        <v>6.7197365760803223</v>
+        <v>6.7194075584411621</v>
       </c>
     </row>
     <row r="120">
@@ -2069,13 +2069,13 @@
         <v>6.2568421363830566</v>
       </c>
       <c r="C120" s="2">
-        <v>6.0914993286132812</v>
+        <v>6.0912785530090332</v>
       </c>
       <c r="D120" s="2">
         <v>6.9154772758483887</v>
       </c>
       <c r="E120" s="2">
-        <v>6.7746739387512207</v>
+        <v>6.772367000579834</v>
       </c>
     </row>
     <row r="121">
@@ -2086,13 +2086,13 @@
         <v>5.8936285972595215</v>
       </c>
       <c r="C121" s="2">
-        <v>5.5327720642089844</v>
+        <v>5.5394320487976074</v>
       </c>
       <c r="D121" s="2">
         <v>6.8374671936035156</v>
       </c>
       <c r="E121" s="2">
-        <v>6.69189453125</v>
+        <v>6.6904230117797852</v>
       </c>
     </row>
     <row r="122">
@@ -2103,13 +2103,13 @@
         <v>8.6180524826049805</v>
       </c>
       <c r="C122" s="2">
-        <v>8.4602832794189453</v>
+        <v>8.4636716842651367</v>
       </c>
       <c r="D122" s="2">
         <v>6.7066268920898438</v>
       </c>
       <c r="E122" s="2">
-        <v>6.5483078956604004</v>
+        <v>6.5467705726623535</v>
       </c>
     </row>
     <row r="123">
@@ -2120,13 +2120,13 @@
         <v>6.842841625213623</v>
       </c>
       <c r="C123" s="2">
-        <v>6.8261590003967285</v>
+        <v>6.8237457275390625</v>
       </c>
       <c r="D123" s="2">
         <v>6.8168668746948242</v>
       </c>
       <c r="E123" s="2">
-        <v>6.6255049705505371</v>
+        <v>6.6267828941345215</v>
       </c>
     </row>
     <row r="124">
@@ -2137,13 +2137,13 @@
         <v>7.2196402549743652</v>
       </c>
       <c r="C124" s="2">
-        <v>7.2614555358886719</v>
+        <v>7.2461938858032227</v>
       </c>
       <c r="D124" s="2">
         <v>6.9036989212036133</v>
       </c>
       <c r="E124" s="2">
-        <v>6.7383933067321777</v>
+        <v>6.7408232688903809</v>
       </c>
     </row>
     <row r="125">
@@ -2154,13 +2154,13 @@
         <v>7.5739192962646484</v>
       </c>
       <c r="C125" s="2">
-        <v>7.4215426445007324</v>
+        <v>7.4264178276062012</v>
       </c>
       <c r="D125" s="2">
         <v>6.8307151794433594</v>
       </c>
       <c r="E125" s="2">
-        <v>6.6746945381164551</v>
+        <v>6.6769933700561523</v>
       </c>
     </row>
     <row r="126">
@@ -2171,13 +2171,13 @@
         <v>6.675290584564209</v>
       </c>
       <c r="C126" s="2">
-        <v>6.3977270126342773</v>
+        <v>6.4045686721801758</v>
       </c>
       <c r="D126" s="2">
         <v>6.8410639762878418</v>
       </c>
       <c r="E126" s="2">
-        <v>6.7050118446350098</v>
+        <v>6.7068414688110352</v>
       </c>
     </row>
     <row r="127">
@@ -2188,13 +2188,13 @@
         <v>6.197932243347168</v>
       </c>
       <c r="C127" s="2">
-        <v>6.0629458427429199</v>
+        <v>6.0694608688354492</v>
       </c>
       <c r="D127" s="2">
         <v>6.66058349609375</v>
       </c>
       <c r="E127" s="2">
-        <v>6.5515217781066895</v>
+        <v>6.5517048835754395</v>
       </c>
     </row>
     <row r="128">
@@ -2205,13 +2205,13 @@
         <v>6.8551449775695801</v>
       </c>
       <c r="C128" s="2">
-        <v>6.5911545753479004</v>
+        <v>6.6026401519775391</v>
       </c>
       <c r="D128" s="2">
         <v>6.711421012878418</v>
       </c>
       <c r="E128" s="2">
-        <v>6.6154899597167969</v>
+        <v>6.6164913177490234</v>
       </c>
     </row>
     <row r="129">
@@ -2222,13 +2222,13 @@
         <v>5.5999865531921387</v>
       </c>
       <c r="C129" s="2">
-        <v>5.5182113647460938</v>
+        <v>5.5168085098266602</v>
       </c>
       <c r="D129" s="2">
         <v>6.7374777793884277</v>
       </c>
       <c r="E129" s="2">
-        <v>6.6402974128723145</v>
+        <v>6.6422243118286133</v>
       </c>
     </row>
     <row r="130">
@@ -2239,13 +2239,13 @@
         <v>5.9867658615112305</v>
       </c>
       <c r="C130" s="2">
-        <v>5.8056259155273438</v>
+        <v>5.8080654144287109</v>
       </c>
       <c r="D130" s="2">
         <v>6.6813745498657227</v>
       </c>
       <c r="E130" s="2">
-        <v>6.5803771018981934</v>
+        <v>6.5829606056213379</v>
       </c>
     </row>
     <row r="131">
@@ -2256,13 +2256,13 @@
         <v>6.9937300682067871</v>
       </c>
       <c r="C131" s="2">
-        <v>7.0788722038269043</v>
+        <v>7.0674409866333008</v>
       </c>
       <c r="D131" s="2">
         <v>6.6321496963500977</v>
       </c>
       <c r="E131" s="2">
-        <v>6.5494318008422852</v>
+        <v>6.5518507957458496</v>
       </c>
     </row>
     <row r="132">
@@ -2273,13 +2273,13 @@
         <v>7.3003807067871094</v>
       </c>
       <c r="C132" s="2">
-        <v>7.4018731117248535</v>
+        <v>7.4068260192871094</v>
       </c>
       <c r="D132" s="2">
         <v>6.8141083717346191</v>
       </c>
       <c r="E132" s="2">
-        <v>6.7598423957824707</v>
+        <v>6.7605867385864258</v>
       </c>
     </row>
     <row r="133">
@@ -2290,13 +2290,13 @@
         <v>7.4541492462158203</v>
       </c>
       <c r="C133" s="2">
-        <v>7.4847240447998047</v>
+        <v>7.4777884483337402</v>
       </c>
       <c r="D133" s="2">
         <v>6.8715853691101074</v>
       </c>
       <c r="E133" s="2">
-        <v>6.827359676361084</v>
+        <v>6.8261752128601074</v>
       </c>
     </row>
     <row r="134">
@@ -2307,13 +2307,13 @@
         <v>7.0689916610717773</v>
       </c>
       <c r="C134" s="2">
-        <v>6.8822588920593262</v>
+        <v>6.8930459022521973</v>
       </c>
       <c r="D134" s="2">
         <v>7.132695198059082</v>
       </c>
       <c r="E134" s="2">
-        <v>7.0888934135437012</v>
+        <v>7.0890994071960449</v>
       </c>
     </row>
     <row r="135">
@@ -2324,13 +2324,13 @@
         <v>6.2322664260864258</v>
       </c>
       <c r="C135" s="2">
-        <v>6.1192188262939453</v>
+        <v>6.1245789527893066</v>
       </c>
       <c r="D135" s="2">
         <v>7.2608222961425781</v>
       </c>
       <c r="E135" s="2">
-        <v>7.2495632171630859</v>
+        <v>7.2487759590148926</v>
       </c>
     </row>
     <row r="136">
@@ -2341,7 +2341,7 @@
         <v>7.8355607986450195</v>
       </c>
       <c r="C136" s="2">
-        <v>7.9566431045532227</v>
+        <v>7.948087215423584</v>
       </c>
       <c r="D136" s="2">
         <v>7.2753996849060059</v>
@@ -2358,13 +2358,13 @@
         <v>7.3724365234375</v>
       </c>
       <c r="C137" s="2">
-        <v>7.1988086700439453</v>
+        <v>7.1929354667663574</v>
       </c>
       <c r="D137" s="2">
-        <v>7.2722768783569336</v>
+        <v>7.4511294364929199</v>
       </c>
       <c r="E137" s="2">
-        <v>7.2324609756469727</v>
+        <v>7.4232020378112793</v>
       </c>
     </row>
     <row r="138">
@@ -2375,13 +2375,13 @@
         <v>7.9499759674072266</v>
       </c>
       <c r="C138" s="2">
-        <v>7.8720145225524902</v>
+        <v>7.8831272125244141</v>
       </c>
       <c r="D138" s="2">
-        <v>7.2462949752807617</v>
+        <v>7.3715124130249023</v>
       </c>
       <c r="E138" s="2">
-        <v>7.1964230537414551</v>
+        <v>7.3022599220275879</v>
       </c>
     </row>
     <row r="139">
@@ -2392,13 +2392,13 @@
         <v>7.1399087905883789</v>
       </c>
       <c r="C139" s="2">
-        <v>7.2516565322875977</v>
+        <v>7.2451553344726562</v>
       </c>
       <c r="D139" s="2">
-        <v>7.2758455276489258</v>
+        <v>7.4249906539916992</v>
       </c>
       <c r="E139" s="2">
-        <v>7.248784065246582</v>
+        <v>7.3691163063049316</v>
       </c>
     </row>
     <row r="140">
@@ -2409,95 +2409,239 @@
         <v>7.1249256134033203</v>
       </c>
       <c r="C140" s="2">
-        <v>7.0943613052368164</v>
+        <v>7.0900144577026367</v>
       </c>
       <c r="D140" s="2">
-        <v>7.4845614433288574</v>
+        <v>7.6462788581848145</v>
       </c>
       <c r="E140" s="2">
-        <v>7.4746966361999512</v>
+        <v>7.6040468215942383</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1">
         <v>45505</v>
       </c>
-      <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="2"/>
+      <c r="B141" s="2">
+        <v>8.8819494247436523</v>
+      </c>
+      <c r="C141" s="2">
+        <v>8.9540872573852539</v>
+      </c>
+      <c r="D141" s="2">
+        <v>7.7529182434082031</v>
+      </c>
+      <c r="E141" s="2">
+        <v>7.7096829414367676</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1">
         <v>45536</v>
       </c>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
+      <c r="B142" s="2">
+        <v>6.7375946044921875</v>
+      </c>
+      <c r="C142" s="2">
+        <v>6.3893089294433594</v>
+      </c>
+      <c r="D142" s="2">
+        <v>7.9473509788513184</v>
+      </c>
+      <c r="E142" s="2">
+        <v>7.916144847869873</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1">
         <v>45566</v>
       </c>
-      <c r="B143" s="2"/>
-      <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
-      <c r="E143" s="2"/>
+      <c r="B143" s="2">
+        <v>7.5502991676330566</v>
+      </c>
+      <c r="C143" s="2">
+        <v>7.4947500228881836</v>
+      </c>
+      <c r="D143" s="2">
+        <v>8.0454492568969727</v>
+      </c>
+      <c r="E143" s="2">
+        <v>8.0461187362670898</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1">
         <v>45597</v>
       </c>
-      <c r="B144" s="2"/>
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
+      <c r="B144" s="2">
+        <v>8.2238588333129883</v>
+      </c>
+      <c r="C144" s="2">
+        <v>8.2389564514160156</v>
+      </c>
+      <c r="D144" s="2">
+        <v>8.072392463684082</v>
+      </c>
+      <c r="E144" s="2">
+        <v>8.0688400268554688</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1">
         <v>45627</v>
       </c>
-      <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
+      <c r="B145" s="2">
+        <v>8.7953166961669922</v>
+      </c>
+      <c r="C145" s="2">
+        <v>8.8988122940063477</v>
+      </c>
+      <c r="D145" s="2">
+        <v>8.1247520446777344</v>
+      </c>
+      <c r="E145" s="2">
+        <v>8.1217689514160156</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1">
         <v>45658</v>
       </c>
-      <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
-      <c r="E146" s="2"/>
+      <c r="B146" s="2">
+        <v>9.1223297119140625</v>
+      </c>
+      <c r="C146" s="2">
+        <v>9.051091194152832</v>
+      </c>
+      <c r="D146" s="2">
+        <v>8.0301017761230469</v>
+      </c>
+      <c r="E146" s="2">
+        <v>8.0177288055419922</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1">
         <v>45689</v>
       </c>
-      <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
+      <c r="B147" s="2">
+        <v>8.8328571319580078</v>
+      </c>
+      <c r="C147" s="2">
+        <v>9.0528907775878906</v>
+      </c>
+      <c r="D147" s="2">
+        <v>8.2147455215454102</v>
+      </c>
+      <c r="E147" s="2">
+        <v>8.2503604888916016</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1">
         <v>45717</v>
       </c>
-      <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
-      <c r="E148" s="2"/>
+      <c r="B148" s="2">
+        <v>7.3823990821838379</v>
+      </c>
+      <c r="C148" s="2">
+        <v>7.4496521949768066</v>
+      </c>
+      <c r="D148" s="2">
+        <v>8.3254871368408203</v>
+      </c>
+      <c r="E148" s="2">
+        <v>8.3762950897216797</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1">
         <v>45748</v>
       </c>
-      <c r="B149" s="2"/>
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
-      <c r="E149" s="2"/>
+      <c r="B149" s="2">
+        <v>7.5961604118347168</v>
+      </c>
+      <c r="C149" s="2">
+        <v>7.566368579864502</v>
+      </c>
+      <c r="D149" s="2">
+        <v>8.3458127975463867</v>
+      </c>
+      <c r="E149" s="2">
+        <v>8.4037628173828125</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
     </row>
   </sheetData>
 </worksheet>
